--- a/Download/Focus_Positivi_ZP.xlsx
+++ b/Download/Focus_Positivi_ZP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="18">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -539,6 +539,20 @@
         <v>3.0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C31" t="n" s="2">
+        <v>46289.0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -562,7 +576,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +584,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +723,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZP.xlsx
+++ b/Download/Focus_Positivi_ZP.xlsx
@@ -550,7 +550,7 @@
         <v>46289.0</v>
       </c>
       <c r="D31" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>
@@ -576,7 +576,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="12">
